--- a/1177 HK Sino.xlsx
+++ b/1177 HK Sino.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CE5C26-505A-464D-B7C8-BD452AF1AF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1D054D-8BEC-435E-80B7-2AAAD77175E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51840" yWindow="1680" windowWidth="22875" windowHeight="18315" activeTab="1" xr2:uid="{C089106D-B5F9-43C6-9823-948CCFB8CE4F}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{C089106D-B5F9-43C6-9823-948CCFB8CE4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -314,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -336,8 +336,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,17 +653,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B886C88C-B397-46FB-B3FD-E7AA45139689}">
   <dimension ref="B2:L14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7265625" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.453125" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
@@ -679,10 +677,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -697,7 +695,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -707,10 +705,10 @@
       </c>
       <c r="K4" s="10">
         <f>+K2*K3</f>
-        <v>57802.067366260002</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>92593.757596270007</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
@@ -726,7 +724,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
       <c r="H6" s="3"/>
       <c r="J6" t="s">
@@ -740,7 +738,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
         <v>30</v>
@@ -759,92 +757,70 @@
       </c>
       <c r="K7" s="10">
         <f>+K4-K5+K6</f>
-        <v>26707.706366260009</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>61499.396596270017</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16" t="s">
+      <c r="D11" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
+      <c r="D12" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>44</v>
       </c>
@@ -863,14 +839,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB25B3E2-C5C5-4C2E-8D1A-B23F6023BD3F}">
   <dimension ref="B2:L14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="9.140625" style="11"/>
+    <col min="1" max="1" width="4.1796875" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="9.1796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
@@ -902,7 +878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:12" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>
@@ -923,7 +899,7 @@
         <v>15874.403</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
@@ -946,7 +922,7 @@
         <v>2844.7800000000007</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>19</v>
       </c>
@@ -969,7 +945,7 @@
         <v>13029.623</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
         <v>21</v>
       </c>
@@ -984,7 +960,7 @@
       </c>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
@@ -999,7 +975,7 @@
       </c>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
@@ -1014,7 +990,7 @@
       </c>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>22</v>
       </c>
@@ -1047,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>23</v>
       </c>
@@ -1080,7 +1056,7 @@
         <v>13029.623</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>25</v>
       </c>
@@ -1095,7 +1071,7 @@
       </c>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
@@ -1116,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>27</v>
       </c>
@@ -1133,7 +1109,7 @@
       </c>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
